--- a/Sindhi Muslim/Classes/26-2-2025/Govt High School sindhi jamaat society.xlsx
+++ b/Sindhi Muslim/Classes/26-2-2025/Govt High School sindhi jamaat society.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\26-2-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C5ADB9-00EC-492D-8BE6-538565E62D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD73CBF0-F2D9-4663-B585-4908B18965D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="390" windowWidth="20460" windowHeight="10890" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Record" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Class - I" sheetId="2" r:id="rId3"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Record'!$A$2:$O$272</definedName>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4997" uniqueCount="1402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4969" uniqueCount="1401">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -3963,9 +3962,6 @@
   </si>
   <si>
     <t xml:space="preserve">Nazeer Ahmed </t>
-  </si>
-  <si>
-    <t>112-08-2014</t>
   </si>
   <si>
     <t>Muhammad Hussan ali</t>
@@ -4671,17 +4667,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="59">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="58">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5285,25 +5271,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="58"/>
-      <tableStyleElement type="headerRow" dxfId="57"/>
-      <tableStyleElement type="totalRow" dxfId="56"/>
-      <tableStyleElement type="firstColumn" dxfId="55"/>
-      <tableStyleElement type="lastColumn" dxfId="54"/>
-      <tableStyleElement type="firstRowStripe" dxfId="53"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="52"/>
+      <tableStyleElement type="wholeTable" dxfId="57"/>
+      <tableStyleElement type="headerRow" dxfId="56"/>
+      <tableStyleElement type="totalRow" dxfId="55"/>
+      <tableStyleElement type="firstColumn" dxfId="54"/>
+      <tableStyleElement type="lastColumn" dxfId="53"/>
+      <tableStyleElement type="firstRowStripe" dxfId="52"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="51"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="51"/>
-      <tableStyleElement type="totalRow" dxfId="50"/>
-      <tableStyleElement type="firstRowStripe" dxfId="49"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="48"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="47"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="46"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="45"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="44"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="43"/>
-      <tableStyleElement type="pageFieldValues" dxfId="42"/>
+      <tableStyleElement type="headerRow" dxfId="50"/>
+      <tableStyleElement type="totalRow" dxfId="49"/>
+      <tableStyleElement type="firstRowStripe" dxfId="48"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="47"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="46"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="45"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="44"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="43"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="42"/>
+      <tableStyleElement type="pageFieldValues" dxfId="41"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5620,7 +5606,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
@@ -8497,7 +8483,7 @@
         <v>108</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>813</v>
@@ -8547,7 +8533,7 @@
         <v>153</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>24</v>
@@ -9576,7 +9562,7 @@
         <v>193</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="F87" s="13" t="s">
         <v>595</v>
@@ -18799,8 +18785,8 @@
       <c r="H286" s="38" t="s">
         <v>775</v>
       </c>
-      <c r="I286" s="14" t="s">
-        <v>1309</v>
+      <c r="I286" s="14">
+        <v>41981</v>
       </c>
       <c r="J286" s="40" t="s">
         <v>776</v>
@@ -18882,7 +18868,7 @@
         <v>779</v>
       </c>
       <c r="E288" s="17" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F288" s="13" t="s">
         <v>806</v>
@@ -20552,7 +20538,7 @@
         <v>605</v>
       </c>
       <c r="E324" s="17" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="F324" s="13" t="s">
         <v>480</v>
@@ -20645,7 +20631,7 @@
         <v>113</v>
       </c>
       <c r="F326" s="13" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="G326" s="38" t="s">
         <v>24</v>
@@ -20683,7 +20669,7 @@
         <v>604</v>
       </c>
       <c r="E327" s="17" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="F327" s="13" t="s">
         <v>230</v>
@@ -20911,7 +20897,7 @@
         <v>907</v>
       </c>
       <c r="F332" s="13" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="G332" s="38" t="s">
         <v>24</v>
@@ -20953,7 +20939,7 @@
         <v>711</v>
       </c>
       <c r="E333" s="17" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="F333" s="13" t="s">
         <v>89</v>
@@ -20998,7 +20984,7 @@
         <v>600</v>
       </c>
       <c r="E334" s="17" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="F334" s="13" t="s">
         <v>910</v>
@@ -21013,7 +20999,7 @@
         <v>41935</v>
       </c>
       <c r="J334" s="55" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="K334" s="38" t="s">
         <v>20</v>
@@ -21046,7 +21032,7 @@
         <v>911</v>
       </c>
       <c r="F335" s="13" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="G335" s="38" t="s">
         <v>24</v>
@@ -21181,7 +21167,7 @@
         <v>103</v>
       </c>
       <c r="F338" s="13" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="G338" s="38" t="s">
         <v>24</v>
@@ -21358,7 +21344,7 @@
         <v>705</v>
       </c>
       <c r="E342" s="17" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="F342" s="13" t="s">
         <v>114</v>
@@ -21451,7 +21437,7 @@
         <v>930</v>
       </c>
       <c r="F344" s="13" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G344" s="38" t="s">
         <v>24</v>
@@ -21493,10 +21479,10 @@
         <v>634</v>
       </c>
       <c r="E345" s="17" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F345" s="13" t="s">
         <v>1322</v>
-      </c>
-      <c r="F345" s="13" t="s">
-        <v>1323</v>
       </c>
       <c r="G345" s="38" t="s">
         <v>17</v>
@@ -21898,10 +21884,10 @@
         <v>709</v>
       </c>
       <c r="E354" s="17" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F354" s="13" t="s">
         <v>1324</v>
-      </c>
-      <c r="F354" s="13" t="s">
-        <v>1325</v>
       </c>
       <c r="G354" s="38" t="s">
         <v>17</v>
@@ -22039,7 +22025,7 @@
         <v>952</v>
       </c>
       <c r="F357" s="13" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="G357" s="38" t="s">
         <v>17</v>
@@ -22126,10 +22112,10 @@
         <v>708</v>
       </c>
       <c r="E359" s="17" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="F359" s="13" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="G359" s="38" t="s">
         <v>17</v>
@@ -22171,7 +22157,7 @@
         <v>641</v>
       </c>
       <c r="E360" s="17" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="F360" s="13" t="s">
         <v>1304</v>
@@ -22216,10 +22202,10 @@
         <v>782</v>
       </c>
       <c r="E361" s="17" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F361" s="13" t="s">
         <v>1330</v>
-      </c>
-      <c r="F361" s="13" t="s">
-        <v>1331</v>
       </c>
       <c r="G361" s="38" t="s">
         <v>17</v>
@@ -22309,7 +22295,7 @@
         <v>959</v>
       </c>
       <c r="F363" s="13" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="G363" s="38" t="s">
         <v>17</v>
@@ -22439,7 +22425,7 @@
         <v>852</v>
       </c>
       <c r="E366" s="17" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F366" s="13" t="s">
         <v>967</v>
@@ -22529,7 +22515,7 @@
         <v>888</v>
       </c>
       <c r="E368" s="17" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="F368" s="13" t="s">
         <v>974</v>
@@ -22802,7 +22788,7 @@
         <v>1063</v>
       </c>
       <c r="F374" s="13" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="G374" s="38" t="s">
         <v>24</v>
@@ -22979,10 +22965,10 @@
         <v>715</v>
       </c>
       <c r="E378" s="17" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F378" s="13" t="s">
         <v>1336</v>
-      </c>
-      <c r="F378" s="13" t="s">
-        <v>1337</v>
       </c>
       <c r="G378" s="38" t="s">
         <v>24</v>
@@ -23024,7 +23010,7 @@
         <v>474</v>
       </c>
       <c r="E379" s="17" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="F379" s="13" t="s">
         <v>113</v>
@@ -23162,7 +23148,7 @@
         <v>1027</v>
       </c>
       <c r="F382" s="13" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="G382" s="38" t="s">
         <v>24</v>
@@ -23249,7 +23235,7 @@
         <v>436</v>
       </c>
       <c r="E384" s="17" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="F384" s="13" t="s">
         <v>285</v>
@@ -23297,7 +23283,7 @@
         <v>851</v>
       </c>
       <c r="F385" s="13" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="G385" s="38" t="s">
         <v>17</v>
@@ -23342,7 +23328,7 @@
         <v>1083</v>
       </c>
       <c r="F386" s="13" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G386" s="38" t="s">
         <v>17</v>
@@ -23387,7 +23373,7 @@
         <v>1085</v>
       </c>
       <c r="F387" s="13" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="G387" s="38" t="s">
         <v>17</v>
@@ -23474,7 +23460,7 @@
         <v>618</v>
       </c>
       <c r="E389" s="17" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F389" s="13" t="s">
         <v>1089</v>
@@ -23564,10 +23550,10 @@
         <v>614</v>
       </c>
       <c r="E391" s="17" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F391" s="13" t="s">
         <v>1345</v>
-      </c>
-      <c r="F391" s="13" t="s">
-        <v>1346</v>
       </c>
       <c r="G391" s="38" t="s">
         <v>17</v>
@@ -23792,7 +23778,7 @@
         <v>942</v>
       </c>
       <c r="F396" s="13" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G396" s="38" t="s">
         <v>17</v>
@@ -23834,10 +23820,10 @@
         <v>613</v>
       </c>
       <c r="E397" s="12" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="F397" s="23" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="G397" s="38" t="s">
         <v>17</v>
@@ -23879,7 +23865,7 @@
         <v>907</v>
       </c>
       <c r="E398" s="17" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F398" s="13" t="s">
         <v>180</v>
@@ -23927,7 +23913,7 @@
         <v>216</v>
       </c>
       <c r="F399" s="13" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G399" s="38" t="s">
         <v>17</v>
@@ -24059,7 +24045,7 @@
         <v>879</v>
       </c>
       <c r="E402" s="17" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F402" s="13" t="s">
         <v>1113</v>
@@ -24104,7 +24090,7 @@
         <v>305</v>
       </c>
       <c r="E403" s="17" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="F403" s="13" t="s">
         <v>792</v>
@@ -24194,7 +24180,7 @@
         <v>789</v>
       </c>
       <c r="E405" s="17" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F405" s="13" t="s">
         <v>911</v>
@@ -24287,7 +24273,7 @@
         <v>855</v>
       </c>
       <c r="F407" s="13" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="G407" s="38" t="s">
         <v>17</v>
@@ -24374,7 +24360,7 @@
         <v>482</v>
       </c>
       <c r="E409" s="17" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="F409" s="13" t="s">
         <v>1127</v>
@@ -24419,7 +24405,7 @@
         <v>331</v>
       </c>
       <c r="E410" s="17" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="F410" s="13" t="s">
         <v>1088</v>
@@ -24690,7 +24676,7 @@
         <v>1140</v>
       </c>
       <c r="F416" s="13" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="G416" s="38" t="s">
         <v>24</v>
@@ -24732,7 +24718,7 @@
         <v>723</v>
       </c>
       <c r="E417" s="17" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="F417" s="13" t="s">
         <v>1122</v>
@@ -24780,7 +24766,7 @@
         <v>1144</v>
       </c>
       <c r="F418" s="13" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="G418" s="38" t="s">
         <v>24</v>
@@ -24823,7 +24809,7 @@
         <v>1145</v>
       </c>
       <c r="F419" s="13" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="G419" s="38" t="s">
         <v>24</v>
@@ -24865,7 +24851,7 @@
         <v>718</v>
       </c>
       <c r="E420" s="17" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="F420" s="13" t="s">
         <v>353</v>
@@ -25087,7 +25073,7 @@
         <v>281</v>
       </c>
       <c r="F425" s="13" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="G425" s="38" t="s">
         <v>24</v>
@@ -25352,7 +25338,7 @@
         <v>622</v>
       </c>
       <c r="E431" s="57" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F431" s="38" t="s">
         <v>1169</v>
@@ -25397,7 +25383,7 @@
         <v>849</v>
       </c>
       <c r="E432" s="57" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="F432" s="38" t="s">
         <v>810</v>
@@ -25577,10 +25563,10 @@
         <v>862</v>
       </c>
       <c r="E436" s="17" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F436" s="13" t="s">
         <v>1363</v>
-      </c>
-      <c r="F436" s="13" t="s">
-        <v>1364</v>
       </c>
       <c r="G436" s="38" t="s">
         <v>17</v>
@@ -25622,7 +25608,7 @@
         <v>870</v>
       </c>
       <c r="E437" s="48" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="F437" s="48" t="s">
         <v>927</v>
@@ -25715,7 +25701,7 @@
         <v>1179</v>
       </c>
       <c r="F439" s="48" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G439" s="38" t="s">
         <v>17</v>
@@ -25753,7 +25739,7 @@
         <v>871</v>
       </c>
       <c r="E440" s="48" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F440" s="48" t="s">
         <v>499</v>
@@ -25929,10 +25915,10 @@
         <v>352</v>
       </c>
       <c r="E444" s="48" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F444" s="48" t="s">
         <v>1367</v>
-      </c>
-      <c r="F444" s="48" t="s">
-        <v>1368</v>
       </c>
       <c r="G444" s="38" t="s">
         <v>17</v>
@@ -26064,10 +26050,10 @@
         <v>726</v>
       </c>
       <c r="E447" s="48" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F447" s="48" t="s">
         <v>1369</v>
-      </c>
-      <c r="F447" s="48" t="s">
-        <v>1370</v>
       </c>
       <c r="G447" s="38" t="s">
         <v>17</v>
@@ -26244,10 +26230,10 @@
         <v>623</v>
       </c>
       <c r="E451" s="48" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F451" s="48" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="G451" s="38" t="s">
         <v>17</v>
@@ -26289,7 +26275,7 @@
         <v>905</v>
       </c>
       <c r="E452" s="48" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="F452" s="48" t="s">
         <v>1202</v>
@@ -26334,7 +26320,7 @@
         <v>737</v>
       </c>
       <c r="E453" s="17" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F453" s="13" t="s">
         <v>780</v>
@@ -26472,7 +26458,7 @@
         <v>1210</v>
       </c>
       <c r="F456" s="13" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="G456" s="38" t="s">
         <v>17</v>
@@ -26649,7 +26635,7 @@
         <v>743</v>
       </c>
       <c r="E460" s="17" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="F460" s="13" t="s">
         <v>1213</v>
@@ -26697,7 +26683,7 @@
         <v>1216</v>
       </c>
       <c r="F461" s="13" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G461" s="38" t="s">
         <v>17</v>
@@ -26742,7 +26728,7 @@
         <v>1217</v>
       </c>
       <c r="F462" s="13" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G462" s="38" t="s">
         <v>17</v>
@@ -26967,7 +26953,7 @@
         <v>1229</v>
       </c>
       <c r="F467" s="13" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="G467" s="38" t="s">
         <v>17</v>
@@ -27012,7 +26998,7 @@
         <v>942</v>
       </c>
       <c r="F468" s="13" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G468" s="38" t="s">
         <v>17</v>
@@ -27098,7 +27084,7 @@
         <v>1231</v>
       </c>
       <c r="F470" s="13" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="G470" s="38" t="s">
         <v>17</v>
@@ -27143,7 +27129,7 @@
         <v>1234</v>
       </c>
       <c r="F471" s="13" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="G471" s="38" t="s">
         <v>17</v>
@@ -27271,10 +27257,10 @@
         <v>738</v>
       </c>
       <c r="E474" s="58" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F474" s="58" t="s">
         <v>1381</v>
-      </c>
-      <c r="F474" s="58" t="s">
-        <v>1382</v>
       </c>
       <c r="G474" s="38" t="s">
         <v>17</v>
@@ -27357,7 +27343,7 @@
         <v>732</v>
       </c>
       <c r="E476" s="17" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="F476" s="13" t="s">
         <v>797</v>
@@ -27447,7 +27433,7 @@
         <v>760</v>
       </c>
       <c r="E478" s="17" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="F478" s="17" t="s">
         <v>787</v>
@@ -27621,7 +27607,7 @@
         <v>850</v>
       </c>
       <c r="E482" s="17" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F482" s="17" t="s">
         <v>1034</v>
@@ -27669,7 +27655,7 @@
         <v>103</v>
       </c>
       <c r="F483" s="48" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="G483" s="38" t="s">
         <v>24</v>
@@ -27840,10 +27826,10 @@
         <v>777</v>
       </c>
       <c r="E487" s="48" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F487" s="48" t="s">
         <v>1387</v>
-      </c>
-      <c r="F487" s="48" t="s">
-        <v>1388</v>
       </c>
       <c r="G487" s="38" t="s">
         <v>24</v>
@@ -27975,7 +27961,7 @@
         <v>854</v>
       </c>
       <c r="E490" s="48" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="F490" s="48" t="s">
         <v>1264</v>
@@ -28016,7 +28002,7 @@
         <v>863</v>
       </c>
       <c r="E491" s="48" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="F491" s="48" t="s">
         <v>1009</v>
@@ -28106,10 +28092,10 @@
         <v>886</v>
       </c>
       <c r="E493" s="48" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F493" s="48" t="s">
         <v>1391</v>
-      </c>
-      <c r="F493" s="48" t="s">
-        <v>1392</v>
       </c>
       <c r="G493" s="38" t="s">
         <v>24</v>
@@ -28907,7 +28893,7 @@
         <v>366</v>
       </c>
       <c r="F511" s="13" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="G511" s="38" t="s">
         <v>17</v>
@@ -29172,10 +29158,10 @@
         <v>895</v>
       </c>
       <c r="E517" s="17" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F517" s="13" t="s">
         <v>1394</v>
-      </c>
-      <c r="F517" s="13" t="s">
-        <v>1395</v>
       </c>
       <c r="G517" s="38" t="s">
         <v>24</v>
@@ -29396,7 +29382,7 @@
         <v>1038</v>
       </c>
       <c r="F522" s="13" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="G522" s="38" t="s">
         <v>24</v>
@@ -29574,7 +29560,7 @@
         <v>59</v>
       </c>
       <c r="F526" s="13" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="G526" s="38" t="s">
         <v>24</v>
@@ -29619,7 +29605,7 @@
         <v>1049</v>
       </c>
       <c r="F527" s="13" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="G527" s="38" t="s">
         <v>24</v>
@@ -29652,119 +29638,119 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="D57:D87">
-    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D88:D111">
-    <cfRule type="duplicateValues" dxfId="40" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112">
-    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:D144">
-    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D145:D168">
-    <cfRule type="duplicateValues" dxfId="37" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D222:D248">
-    <cfRule type="duplicateValues" dxfId="36" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D249:D270 D272">
-    <cfRule type="duplicateValues" dxfId="35" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D321:D349">
-    <cfRule type="duplicateValues" dxfId="34" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D373:D397">
-    <cfRule type="duplicateValues" dxfId="33" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D408:D434">
-    <cfRule type="duplicateValues" dxfId="32" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D435:D436">
-    <cfRule type="duplicateValues" dxfId="31" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D453:D467">
-    <cfRule type="duplicateValues" dxfId="30" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D468">
-    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D469:D473">
-    <cfRule type="duplicateValues" dxfId="26" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D474">
-    <cfRule type="duplicateValues" dxfId="25" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D475:D481">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D482">
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D494:D499 D350:D368">
-    <cfRule type="duplicateValues" dxfId="20" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D494:D527 D273:D407">
-    <cfRule type="duplicateValues" dxfId="19" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D500">
-    <cfRule type="duplicateValues" dxfId="18" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D501:D527 D369:D372">
-    <cfRule type="duplicateValues" dxfId="17" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D528:D1048576 D1:D272">
-    <cfRule type="duplicateValues" dxfId="16" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E408:E434">
-    <cfRule type="duplicateValues" dxfId="15" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M385">
-    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M445">
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M453:M493">
-    <cfRule type="duplicateValues" dxfId="12" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M517:M527 M446:M452 M273:M384 M494:M515 M386:M398 M400:M444">
-    <cfRule type="duplicateValues" dxfId="11" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M528:M1048576 M129:M170 M1:M127 M172:M221 M223:M272">
-    <cfRule type="duplicateValues" dxfId="10" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N315">
-    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N377">
-    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N421">
-    <cfRule type="duplicateValues" dxfId="7" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N436">
-    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N445">
-    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N451">
-    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N453:N493">
-    <cfRule type="duplicateValues" dxfId="3" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N512:N518 N437:N444 N370:N371 N373:N376 N386 N388 N520:N527 N392:N420 N378:N383 N422:N435 N446:N450 N452 N273:N314 N316:N368 N494:N510">
-    <cfRule type="duplicateValues" dxfId="2" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N528:N1048576 N124:N130 N1:N122 N132:N140 N142:N143 N145:N148 N160 N150:N158 N164:N204 N206:N217 N219:N220 N222:N230 N232 N234:N237 N239:N272">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -29772,238 +29758,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B05AFE0D-F275-41BA-95F8-EDF5E9C35463}">
-  <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="11">
-        <v>772</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="15">
-        <v>839</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="15">
-        <v>673</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="15">
-        <v>523</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="15">
-        <v>668</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="15">
-        <v>665</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="15">
-        <v>656</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="15">
-        <v>840</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="15">
-        <v>679</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="15">
-        <v>675</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="15"/>
-      <c r="B12" s="17" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="15">
-        <v>774</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="15">
-        <v>655</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="15">
-        <v>653</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="15">
-        <v>657</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="15">
-        <v>672</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="15">
-        <v>702</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="15">
-        <v>659</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="15">
-        <v>661</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="15">
-        <v>660</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="15">
-        <v>654</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="15">
-        <v>841</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="15">
-        <v>522</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="15">
-        <v>676</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="15">
-        <v>658</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="15">
-        <v>785</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>366</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B27">
-    <sortCondition ref="B1:B27"/>
-  </sortState>
-  <conditionalFormatting sqref="A1:A27">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
